--- a/base/StructureDefinition-SGGroupDefinition.xlsx
+++ b/base/StructureDefinition-SGGroupDefinition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,7 +260,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}grp-1:Can only have members if group is "actual" {member.empty() or (actual = true)}gdf-1:Group definition must have either an expression or characteristics, but not both {extension('http://hl7.org/fhir/StructureDefinition/cqf-expression').exists() xor characteristic.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}grp-1:Can only have members if group is "actual" {member.empty() or (actual = true)}gdf-1:Group definition must have either a characteristicExpression or characteristics, but not both {extension('http://hl7.org/fhir/StructureDefinition/characteristicExpression').exists() xor characteristic.exists()}</t>
   </si>
   <si>
     <t>Entity[determinerCode="GRP" or determinerCode="GRP_KIND"]</t>
@@ -352,7 +352,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -453,26 +453,27 @@
     <t>A reference to a Library containing the formal logic used by the artifact.</t>
   </si>
   <si>
-    <t>For questionnaires, see additional guidance and examples in the [SDC implementation guide](http://hl7.org/fhir/uv/sdc/behavior.html#cqf-library).</t>
-  </si>
-  <si>
-    <t>Group.extension:expression</t>
-  </si>
-  <si>
-    <t>expression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {cqf-expression}
+    <t>For questionnaires, see additional guidance and examples in the [SDC implementation guide](http://hl7.org/fhir/uv/sdc/2025Jan/behavior.html#cqf-library).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>An dynamic expression</t>
-  </si>
-  <si>
-    <t>An expression that, when evaluated, provides the value for the element on which it appears.</t>
-  </si>
-  <si>
-    <t>For questionnaires, see additional guidance and examples in the [SDC implementation guide](http://hl7.org/fhir/uv/sdc/behavior.html#cqf-expression).</t>
+    <t>Group.extension:characteristicExpression</t>
+  </si>
+  <si>
+    <t>characteristicExpression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {characteristicExpression}
+</t>
+  </si>
+  <si>
+    <t>Criteria for group membership</t>
+  </si>
+  <si>
+    <t>An expression that defines the criteria for group membership. This extension can only be used on a Group resource with a membership of `definitional`. When this expression is used, the Group resource cannot have any characteristic elements; this mechanism is exclusive with characteristics. The result of the expression SHALL be boolean-valued. The expression SHALL be parameterized with a `%context` variable that represents the subject being tested for membership. If evaluation of the expression results in `true`, the subject is considered a member of the group.</t>
   </si>
   <si>
     <t>Group.modifierExtension</t>
@@ -609,7 +610,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -682,7 +683,7 @@
     <t>Group.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -839,7 +840,7 @@
     <t>Group.managingEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|RelatedPerson|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -864,14 +865,66 @@
     <t>profile</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {artifact-canonicalReference}
+    <t xml:space="preserve">Extension {artifact-reference}
 </t>
   </si>
   <si>
     <t>The artifact</t>
   </si>
   <si>
-    <t>A reference to a canonical resource.</t>
+    <t>A reference to a resource, canonical resource, or non-FHIR resource.</t>
+  </si>
+  <si>
+    <t>Group.managingEntity.extension:profile.id</t>
+  </si>
+  <si>
+    <t>Group.managingEntity.extension.id</t>
+  </si>
+  <si>
+    <t>Group.managingEntity.extension:profile.extension</t>
+  </si>
+  <si>
+    <t>Group.managingEntity.extension.extension</t>
+  </si>
+  <si>
+    <t>Group.managingEntity.extension:profile.url</t>
+  </si>
+  <si>
+    <t>Group.managingEntity.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/artifact-reference</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Group.managingEntity.extension:profile.value[x]</t>
+  </si>
+  <si>
+    <t>Group.managingEntity.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
   </si>
   <si>
     <t>Group.managingEntity.reference</t>
@@ -909,7 +962,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1033,9 +1086,75 @@
     <t>Value of descriptive member characteristic; e.g. red, male, pneumonia, Caucasian, etc.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>./value</t>
   </si>
   <si>
+    <t>Group.characteristic.value[x]:valueReference</t>
+  </si>
+  <si>
+    <t>valueReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference
+</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x]:valueReference.id</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x].id</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x]:valueReference.extension</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x].extension</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x]:valueReference.extension:valueCanonical</t>
+  </si>
+  <si>
+    <t>valueCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/crmi/StructureDefinition/crmi-groupCharacteristicValueCanonical}
+</t>
+  </si>
+  <si>
+    <t>Instances that conform to the referenced profile</t>
+  </si>
+  <si>
+    <t>Instances that conform to the referenced profile are included (or excluded if characteristic.exclude is true) in the cohort.</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x]:valueReference.reference</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x].reference</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x]:valueReference.type</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x].type</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x]:valueReference.identifier</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x].identifier</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x]:valueReference.display</t>
+  </si>
+  <si>
+    <t>Group.characteristic.value[x].display</t>
+  </si>
+  <si>
     <t>Group.characteristic.exclude</t>
   </si>
   <si>
@@ -1090,7 +1209,7 @@
     <t>Group.member.entity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Device|Medication|Substance|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Medication|4.0.1|Substance|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1115,10 +1234,6 @@
     <t>Group.member.entity.extension.id</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Group.member.entity.extension:profile.extension</t>
   </si>
   <si>
@@ -1131,46 +1246,27 @@
     <t>Group.member.entity.extension.url</t>
   </si>
   <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/artifact-canonicalReference</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
     <t>Group.member.entity.extension:profile.value[x]</t>
   </si>
   <si>
     <t>Group.member.entity.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 gdf-2:Reference must be to a structure definition {resolve().conformsTo('http://hl7.org/fhir/StructureDefinition/StructureDefinition')}</t>
+  </si>
+  <si>
+    <t>Group.member.entity.extension:nonCanonicalReference</t>
+  </si>
+  <si>
+    <t>nonCanonicalReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {artifact-uriReference}
+</t>
+  </si>
+  <si>
+    <t>Create a reference, following canonical reference semantics, to an artifact that uses the artifact-url and artifact-version extensions to provide a canonical identifier.</t>
   </si>
   <si>
     <t>Group.member.entity.reference</t>
@@ -1531,20 +1627,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL61"/>
+  <dimension ref="A1:AL74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.6171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.43359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.0625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="20.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.94921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="99.2265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1553,24 +1649,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.8125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.56640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="44.3984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.0703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="38.78125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="182.2109375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="32.84375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="161.578125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2547,7 +2643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>135</v>
       </c>
@@ -2645,7 +2741,7 @@
         <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>134</v>
@@ -2657,15 +2753,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>21</v>
@@ -2687,17 +2783,15 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>146</v>
       </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
@@ -2755,7 +2849,7 @@
         <v>75</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>134</v>
@@ -2877,7 +2971,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>154</v>
       </c>
@@ -3199,7 +3293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>172</v>
       </c>
@@ -3419,7 +3513,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>192</v>
       </c>
@@ -3529,7 +3623,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>200</v>
       </c>
@@ -3851,7 +3945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>220</v>
       </c>
@@ -3961,7 +4055,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>228</v>
       </c>
@@ -4071,7 +4165,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>238</v>
       </c>
@@ -4179,7 +4273,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>244</v>
       </c>
@@ -4287,7 +4381,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>252</v>
       </c>
@@ -4505,7 +4599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>264</v>
       </c>
@@ -4524,7 +4618,7 @@
         <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -4827,7 +4921,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>271</v>
       </c>
@@ -4940,7 +5034,7 @@
         <v>276</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4960,20 +5054,18 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5022,7 +5114,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>165</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -5031,13 +5123,13 @@
         <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
@@ -5045,10 +5137,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5059,7 +5151,7 @@
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5068,20 +5160,18 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>129</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5106,46 +5196,46 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>288</v>
+        <v>171</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>21</v>
@@ -5153,10 +5243,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5164,7 +5254,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>83</v>
@@ -5176,19 +5266,19 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>155</v>
+        <v>97</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5196,7 +5286,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>21</v>
+        <v>285</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>21</v>
@@ -5238,10 +5328,10 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>83</v>
@@ -5250,10 +5340,10 @@
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>294</v>
+        <v>126</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
@@ -5261,10 +5351,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5272,7 +5362,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>83</v>
@@ -5284,20 +5374,18 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>162</v>
+        <v>289</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5346,7 +5434,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5369,10 +5457,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5383,32 +5471,30 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="I36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>301</v>
+        <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5456,22 +5542,22 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>306</v>
+        <v>126</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
@@ -5479,10 +5565,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5502,18 +5588,20 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>163</v>
+        <v>300</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5538,13 +5626,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -5562,7 +5650,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>165</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5574,10 +5662,10 @@
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
@@ -5585,21 +5673,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -5608,19 +5696,19 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>168</v>
+        <v>307</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>169</v>
+        <v>308</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>151</v>
+        <v>309</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5670,22 +5758,22 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>171</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>166</v>
+        <v>311</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
@@ -5693,46 +5781,44 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -5780,19 +5866,19 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>126</v>
@@ -5801,12 +5887,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5814,13 +5900,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -5829,17 +5915,19 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>183</v>
+        <v>318</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -5864,10 +5952,10 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>21</v>
@@ -5888,13 +5976,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -5903,7 +5991,7 @@
         <v>95</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
@@ -5911,10 +5999,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5922,7 +6010,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>83</v>
@@ -5937,20 +6025,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>320</v>
+        <v>162</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>321</v>
+        <v>163</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -5974,10 +6058,10 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
       <c r="Z41" t="s" s="2">
         <v>21</v>
@@ -5998,10 +6082,10 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>319</v>
+        <v>165</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>83</v>
@@ -6010,10 +6094,10 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>326</v>
+        <v>166</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -6021,21 +6105,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6047,20 +6131,18 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>221</v>
+        <v>128</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>328</v>
+        <v>168</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>329</v>
+        <v>169</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6108,22 +6190,22 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>327</v>
+        <v>171</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>332</v>
+        <v>166</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -6131,42 +6213,46 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>208</v>
+        <v>128</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6214,22 +6300,22 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6237,10 +6323,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6248,10 +6334,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6263,17 +6349,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>301</v>
+        <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6298,10 +6384,10 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>21</v>
@@ -6322,22 +6408,22 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>340</v>
+        <v>250</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6345,10 +6431,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6356,13 +6442,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -6371,16 +6457,20 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>163</v>
+        <v>338</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6404,10 +6494,10 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="Z45" t="s" s="2">
         <v>21</v>
@@ -6416,22 +6506,20 @@
         <v>21</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>165</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>83</v>
@@ -6440,35 +6528,37 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>166</v>
+        <v>344</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="D46" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -6477,18 +6567,20 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>128</v>
+        <v>347</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>168</v>
+        <v>338</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>169</v>
+        <v>339</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6536,22 +6628,22 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>171</v>
+        <v>336</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>166</v>
+        <v>344</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
@@ -6559,46 +6651,42 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>311</v>
+        <v>163</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -6646,22 +6734,22 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>313</v>
+        <v>165</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
@@ -6669,21 +6757,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -6695,15 +6783,17 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>346</v>
+        <v>168</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -6740,47 +6830,49 @@
         <v>21</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>344</v>
+        <v>171</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>21</v>
       </c>
@@ -6792,7 +6884,7 @@
         <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -6801,13 +6893,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>162</v>
+        <v>354</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>163</v>
+        <v>355</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>164</v>
+        <v>356</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6858,22 +6950,22 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
@@ -6881,21 +6973,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -6904,19 +6996,19 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>168</v>
+        <v>294</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>169</v>
+        <v>295</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>151</v>
+        <v>296</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6954,34 +7046,34 @@
         <v>21</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>171</v>
+        <v>297</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
@@ -6989,14 +7081,12 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7008,24 +7098,26 @@
         <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="I51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K51" t="s" s="2">
-        <v>273</v>
+        <v>97</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7050,13 +7142,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7074,22 +7166,22 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>171</v>
+        <v>305</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7097,10 +7189,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7120,18 +7212,20 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>163</v>
+        <v>307</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7180,7 +7274,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>165</v>
+        <v>310</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7189,13 +7283,13 @@
         <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>166</v>
+        <v>311</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7203,10 +7297,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7217,7 +7311,7 @@
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7226,18 +7320,20 @@
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>129</v>
+        <v>313</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7274,34 +7370,34 @@
         <v>21</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>171</v>
+        <v>316</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
@@ -7309,10 +7405,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7335,24 +7431,26 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>361</v>
+        <v>21</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>21</v>
@@ -7394,7 +7492,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -7406,10 +7504,10 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>126</v>
+        <v>370</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
@@ -7417,10 +7515,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7428,7 +7526,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>83</v>
@@ -7443,13 +7541,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>365</v>
+        <v>208</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7500,7 +7598,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7509,24 +7607,24 @@
         <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>370</v>
+        <v>95</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7537,30 +7635,30 @@
         <v>74</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>162</v>
+        <v>318</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>277</v>
+        <v>375</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -7608,22 +7706,22 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>280</v>
+        <v>374</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>126</v>
+        <v>378</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
@@ -7631,10 +7729,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7654,20 +7752,18 @@
         <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>283</v>
+        <v>163</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -7692,13 +7788,13 @@
         <v>21</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
@@ -7716,7 +7812,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>288</v>
+        <v>165</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -7728,10 +7824,10 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
@@ -7739,21 +7835,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -7762,19 +7858,19 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>290</v>
+        <v>168</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>291</v>
+        <v>169</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>292</v>
+        <v>151</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7824,22 +7920,22 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>293</v>
+        <v>171</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>294</v>
+        <v>166</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
@@ -7847,44 +7943,46 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -7932,19 +8030,19 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>126</v>
@@ -7953,12 +8051,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7966,13 +8064,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -7981,24 +8079,20 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>208</v>
+        <v>383</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q60" t="s" s="2">
-        <v>379</v>
-      </c>
+      <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8042,10 +8136,10 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>83</v>
@@ -8065,10 +8159,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8091,100 +8185,1498 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="D68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q73" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="R73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K74" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q61" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="R61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
+      <c r="L74" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AK74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL61">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AL74">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
